--- a/data/trans_bre/IQ2606_R2-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IQ2606_R2-Edad-trans_bre.xlsx
@@ -606,7 +606,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-2,35</t>
+          <t>-1,75</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -621,7 +621,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-2,41%</t>
+          <t>-1,8%</t>
         </is>
       </c>
     </row>
@@ -634,32 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-6,31; 10,47</t>
+          <t>-6,14; 10,72</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-14,06; 3,78</t>
+          <t>-15,79; 2,96</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-11,96; 5,64</t>
+          <t>-10,21; 6,2</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-7,58; 14,37</t>
+          <t>-7,33; 14,41</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-17,9; 5,16</t>
+          <t>-20,0; 4,05</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-12,31; 5,84</t>
+          <t>-10,47; 6,75</t>
         </is>
       </c>
     </row>
@@ -686,7 +686,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>10,63</t>
+          <t>9,26</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -701,7 +701,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>10,66%</t>
         </is>
       </c>
     </row>
@@ -714,32 +714,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-2,62; 10,83</t>
+          <t>-2,96; 10,65</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-8,63; 2,85</t>
+          <t>-9,23; 2,97</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,27; 20,78</t>
+          <t>0,46; 19,1</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-3,63; 16,74</t>
+          <t>-4,05; 16,41</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-10,28; 3,6</t>
+          <t>-10,87; 3,74</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,47; 27,08</t>
+          <t>0,54; 25,18</t>
         </is>
       </c>
     </row>
@@ -766,7 +766,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-11,59</t>
+          <t>-12,56</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -781,7 +781,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-13,03%</t>
+          <t>-14,07%</t>
         </is>
       </c>
     </row>
@@ -794,32 +794,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,34; 13,78</t>
+          <t>-4,73; 13,77</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,28; 12,13</t>
+          <t>-3,13; 12,32</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-25,69; 1,88</t>
+          <t>-25,91; 0,8</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-7,57; 29,36</t>
+          <t>-8,27; 29,03</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-4,34; 18,2</t>
+          <t>-4,16; 18,08</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-28,02; 2,23</t>
+          <t>-28,31; 0,75</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-3,72</t>
+          <t>-3,92</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-4,61%</t>
+          <t>-4,86%</t>
         </is>
       </c>
     </row>
@@ -874,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,99; 15,46</t>
+          <t>-1,69; 15,98</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-4,76; 14,04</t>
+          <t>-4,03; 13,38</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-17,85; 9,21</t>
+          <t>-16,0; 8,38</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-2,66; 57,57</t>
+          <t>-4,59; 58,81</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-7,27; 25,82</t>
+          <t>-6,35; 24,54</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-20,8; 12,32</t>
+          <t>-18,65; 11,09</t>
         </is>
       </c>
     </row>
@@ -926,7 +926,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-2,02</t>
+          <t>-2,93</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -941,7 +941,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-2,36%</t>
+          <t>-3,42%</t>
         </is>
       </c>
     </row>
@@ -954,32 +954,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,44; 8,91</t>
+          <t>0,1; 8,53</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-4,14; 3,67</t>
+          <t>-3,85; 3,52</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-8,95; 4,45</t>
+          <t>-9,98; 3,72</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,7; 16,07</t>
+          <t>0,27; 15,37</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-5,44; 5,13</t>
+          <t>-5,16; 4,93</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-10,12; 5,39</t>
+          <t>-11,35; 4,58</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IQ2606_R2-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IQ2606_R2-Edad-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:H19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -520,7 +529,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si el verano pasado emplearon crema solar con factor de protección de 50 o más, siempre o casi siempre</t>
+          <t>Menores que el verano pasado emplearon crema solar con factor de protección de 50 o más, siempre o casi siempre</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -594,239 +603,163 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>2,05</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>-6,19</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-1,75</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2,61%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-8,08%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>-1,8%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>2.054354107035716</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>-6.189862902257715</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>-1.748670063502655</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>0.02605372549856301</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>-0.08075684294565223</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>-0.01799161208924704</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-6,14; 10,72</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-15,79; 2,96</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-10,21; 6,2</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-7,33; 14,41</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>-20,0; 4,05</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-10,47; 6,75</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-6.137107520317472</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-15.78929186067259</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-10.20904147776558</v>
+      </c>
+      <c r="F5" s="6" t="n">
+        <v>-0.07332881104406828</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>-0.2000101490042951</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>-0.1047437320237817</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>10.72487010191154</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>2.959394661648974</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>6.200814995405281</v>
+      </c>
+      <c r="F6" s="6" t="n">
+        <v>0.1441478169678169</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>0.04054502224662349</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>0.06746647218706205</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>3-7</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>4,11</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>-3,05</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>9,26</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>5,98%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-3,72%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>10,66%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-2,96; 10,65</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-9,23; 2,97</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>0,46; 19,1</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-4,05; 16,41</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-10,87; 3,74</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0,54; 25,18</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>4.113339975787711</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>-3.052924027246651</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>9.25712380921453</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>0.05984692118586713</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>-0.03716566722129919</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>0.1066020329275096</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>8-11</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>4,46</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>3,92</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-12,56</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>8,46%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>5,43%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>-14,07%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-2.955882538353473</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-9.225711846400777</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>0.4616854710938828</v>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>-0.04054246647264877</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.1086701966771525</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>0.00538905189726127</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-4,73; 13,77</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-3,13; 12,32</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-25,91; 0,8</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-8,27; 29,03</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-4,16; 18,08</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-28,31; 0,75</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>10.6471987511019</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>2.965532334570017</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>19.09909320188702</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>0.1640957737050631</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>0.03739325075759652</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>0.2518202727456422</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>12-15</t>
+          <t>8-11</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -834,157 +767,243 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>7,01</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>4,68</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-3,92</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>22,57%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>7,88%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>-4,86%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>4.455056091960142</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>3.924152473868237</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>-12.56430669012714</v>
+      </c>
+      <c r="F10" s="6" t="n">
+        <v>0.08456057855075531</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>0.05427018561399317</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>-0.1406854533913714</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-1,69; 15,98</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-4,03; 13,38</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-16,0; 8,38</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-4,59; 58,81</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-6,35; 24,54</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-18,65; 11,09</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-4.731115840115812</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-3.12651969581357</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-25.91194429678259</v>
+      </c>
+      <c r="F11" s="6" t="n">
+        <v>-0.08273144183441025</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>-0.0416061413551257</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>-0.2831472063184312</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>13.77241864976523</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>12.31701249490858</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0.7996191339440257</v>
+      </c>
+      <c r="F12" s="6" t="n">
+        <v>0.2902844862425116</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>0.1808039731502568</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>0.007457614949975804</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>7.013166251664538</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>4.675843556227988</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>-3.920956748418625</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>0.2256660381286863</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>0.07875449695332119</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>-0.04857596373573821</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-1.689448510849197</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-4.029068888452385</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-16.00193618848358</v>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>-0.04588573443719177</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.06349057020288479</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.1864926453271656</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>15.97915916137831</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>13.38453490741076</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>8.382059639147302</v>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>0.5880568455118452</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>0.2453702070129737</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>0.1109208357271671</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>4,55</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>-0,34</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-2,93</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>7,9%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-0,46%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>-3,42%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>0,1; 8,53</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-3,85; 3,52</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>-9,98; 3,72</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>0,27; 15,37</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>-5,16; 4,93</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-11,35; 4,58</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="C16" s="5" t="n">
+        <v>4.547836484341872</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>-0.3351055993549013</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>-2.929035505774136</v>
+      </c>
+      <c r="F16" s="6" t="n">
+        <v>0.07899652103885399</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>-0.004566435591841512</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>-0.03418950440371978</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>0.1008196889340038</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-3.854760058914387</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-9.980223839079811</v>
+      </c>
+      <c r="F17" s="6" t="n">
+        <v>0.002726308143434902</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>-0.05163330710970351</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>-0.1135236177208179</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>8.534949840903913</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>3.520854276043286</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>3.723646708124626</v>
+      </c>
+      <c r="F18" s="6" t="n">
+        <v>0.1537358137930534</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>0.04932372641546322</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>0.0458041531729814</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -993,13 +1012,13 @@
   </sheetData>
   <mergeCells count="8">
     <mergeCell ref="C1:E1"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="F1:H1"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
